--- a/Assets/ArtRes/Excel/游戏初始化配置表.xlsx
+++ b/Assets/ArtRes/Excel/游戏初始化配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13070" windowHeight="4410"/>
+    <workbookView windowWidth="13070" windowHeight="4420"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerInfo" sheetId="1" r:id="rId1"/>
@@ -1162,19 +1162,19 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>10</v>
       </c>
       <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
       <c r="G5">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1254,7 +1254,7 @@
         <v>21</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1271,13 +1271,13 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1288,7 +1288,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1305,7 +1305,7 @@
         <v>24</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -1406,10 +1406,10 @@
         <v>33</v>
       </c>
       <c r="C5">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1426,7 +1426,7 @@
         <v>34</v>
       </c>
       <c r="C6">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -1435,7 +1435,7 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
